--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/192.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/192.xlsx
@@ -426,13 +426,13 @@
         <v>-12.14261494936974</v>
       </c>
       <c r="E2">
-        <v>-14.95160130919671</v>
+        <v>-21.71218279761783</v>
       </c>
       <c r="F2">
-        <v>0.8078912943490073</v>
+        <v>-0.3873450215334249</v>
       </c>
       <c r="G2">
-        <v>-10.11788574997575</v>
+        <v>-16.3371692953257</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.84148776348145</v>
       </c>
       <c r="E3">
-        <v>-14.32192152690416</v>
+        <v>-23.36057450725389</v>
       </c>
       <c r="F3">
-        <v>0.8269749506300527</v>
+        <v>-1.188796028953669</v>
       </c>
       <c r="G3">
-        <v>-9.54101656866667</v>
+        <v>-15.41115011817185</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.46887436428025</v>
       </c>
       <c r="E4">
-        <v>-15.37210634860097</v>
+        <v>-23.48510301399081</v>
       </c>
       <c r="F4">
-        <v>1.070111817591978</v>
+        <v>-0.9620592285990768</v>
       </c>
       <c r="G4">
-        <v>-9.98621873278786</v>
+        <v>-14.70410863098585</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.05084910235525</v>
       </c>
       <c r="E5">
-        <v>-15.6134151430477</v>
+        <v>-22.29401925201935</v>
       </c>
       <c r="F5">
-        <v>0.9381273503051702</v>
+        <v>-0.919436951296855</v>
       </c>
       <c r="G5">
-        <v>-10.25096305956338</v>
+        <v>-15.77582822786857</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.57648205939155</v>
       </c>
       <c r="E6">
-        <v>-15.53557067485584</v>
+        <v>-24.72646642286944</v>
       </c>
       <c r="F6">
-        <v>1.070914756491106</v>
+        <v>-1.287347672512593</v>
       </c>
       <c r="G6">
-        <v>-9.408687442370923</v>
+        <v>-15.8955822469334</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.04498904198399</v>
       </c>
       <c r="E7">
-        <v>-17.01011879581144</v>
+        <v>-23.62389168537789</v>
       </c>
       <c r="F7">
-        <v>1.364329535150488</v>
+        <v>-1.19578254759963</v>
       </c>
       <c r="G7">
-        <v>-9.028279275544348</v>
+        <v>-14.59717966534016</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.450072492030113</v>
       </c>
       <c r="E8">
-        <v>-16.04631914428495</v>
+        <v>-24.32859922502953</v>
       </c>
       <c r="F8">
-        <v>1.044503292939323</v>
+        <v>-0.4323579029150025</v>
       </c>
       <c r="G8">
-        <v>-9.363203857206875</v>
+        <v>-12.81685434850414</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.796894045101673</v>
       </c>
       <c r="E9">
-        <v>-17.60249300922881</v>
+        <v>-25.32815117884658</v>
       </c>
       <c r="F9">
-        <v>1.082360199141987</v>
+        <v>-0.5426836081022608</v>
       </c>
       <c r="G9">
-        <v>-8.092027202128603</v>
+        <v>-12.80104318300858</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.089731253606463</v>
       </c>
       <c r="E10">
-        <v>-18.99090502608451</v>
+        <v>-24.9311308056461</v>
       </c>
       <c r="F10">
-        <v>1.04224334459799</v>
+        <v>-0.8876305935441269</v>
       </c>
       <c r="G10">
-        <v>-7.4758221187219</v>
+        <v>-13.96451786005774</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.334495952536266</v>
       </c>
       <c r="E11">
-        <v>-19.08922725373905</v>
+        <v>-28.33610852590947</v>
       </c>
       <c r="F11">
-        <v>1.095630071007454</v>
+        <v>-1.084649944248456</v>
       </c>
       <c r="G11">
-        <v>-6.999659732717447</v>
+        <v>-13.97566446688847</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.541699411987249</v>
       </c>
       <c r="E12">
-        <v>-19.54932926986637</v>
+        <v>-27.1609015938089</v>
       </c>
       <c r="F12">
-        <v>1.204663472167714</v>
+        <v>-0.6536934742449888</v>
       </c>
       <c r="G12">
-        <v>-7.272332816059518</v>
+        <v>-12.63254303615075</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.723836240308538</v>
       </c>
       <c r="E13">
-        <v>-19.96550508811929</v>
+        <v>-27.56369124289515</v>
       </c>
       <c r="F13">
-        <v>1.435477523401605</v>
+        <v>-0.3927391238814116</v>
       </c>
       <c r="G13">
-        <v>-6.041899044933057</v>
+        <v>-13.79370860768628</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.911038516736104</v>
       </c>
       <c r="E14">
-        <v>-22.15120929571345</v>
+        <v>-25.61036567900459</v>
       </c>
       <c r="F14">
-        <v>1.575893640982213</v>
+        <v>-1.095931473337089</v>
       </c>
       <c r="G14">
-        <v>-5.608826719667757</v>
+        <v>-12.22220422710363</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.127414922157712</v>
       </c>
       <c r="E15">
-        <v>-21.34473788816145</v>
+        <v>-29.45406648960508</v>
       </c>
       <c r="F15">
-        <v>2.011531545671719</v>
+        <v>-0.5772796638250355</v>
       </c>
       <c r="G15">
-        <v>-4.778925921701099</v>
+        <v>-10.89998889144641</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.39614194955239</v>
       </c>
       <c r="E16">
-        <v>-22.86468396104394</v>
+        <v>-29.90214540724204</v>
       </c>
       <c r="F16">
-        <v>2.041164267055506</v>
+        <v>-0.4176009311949378</v>
       </c>
       <c r="G16">
-        <v>-5.297109062235521</v>
+        <v>-10.29120605113876</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.737579408718481</v>
       </c>
       <c r="E17">
-        <v>-23.27960539199674</v>
+        <v>-30.21759211390534</v>
       </c>
       <c r="F17">
-        <v>1.888694563752489</v>
+        <v>0.04558474604067968</v>
       </c>
       <c r="G17">
-        <v>-5.047540276212024</v>
+        <v>-10.78877442460014</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.17147905691689</v>
       </c>
       <c r="E18">
-        <v>-24.61277455443287</v>
+        <v>-26.87759120294103</v>
       </c>
       <c r="F18">
-        <v>2.164653735811898</v>
+        <v>-0.1496561029206108</v>
       </c>
       <c r="G18">
-        <v>-4.094351451817367</v>
+        <v>-10.1927140107999</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.714351220186087</v>
       </c>
       <c r="E19">
-        <v>-26.12271722823242</v>
+        <v>-31.18030040319599</v>
       </c>
       <c r="F19">
-        <v>2.325189253342248</v>
+        <v>0.128395144653093</v>
       </c>
       <c r="G19">
-        <v>-3.584524128224065</v>
+        <v>-11.52330833721701</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.371398342471407</v>
       </c>
       <c r="E20">
-        <v>-25.77529270236395</v>
+        <v>-32.9647523786295</v>
       </c>
       <c r="F20">
-        <v>2.555089506262931</v>
+        <v>0.2645479259093377</v>
       </c>
       <c r="G20">
-        <v>-3.957758342867038</v>
+        <v>-9.806300514365088</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.142181803223207</v>
       </c>
       <c r="E21">
-        <v>-26.61316454868514</v>
+        <v>-34.19858040675937</v>
       </c>
       <c r="F21">
-        <v>2.901143502139689</v>
+        <v>0.114853667223128</v>
       </c>
       <c r="G21">
-        <v>-3.844640312335681</v>
+        <v>-8.66288443273837</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.021740377542293</v>
       </c>
       <c r="E22">
-        <v>-26.9273998885514</v>
+        <v>-33.43972816763502</v>
       </c>
       <c r="F22">
-        <v>3.103724828019041</v>
+        <v>0.1750020260385604</v>
       </c>
       <c r="G22">
-        <v>-2.8930173759811</v>
+        <v>-9.41918849282149</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.008316866562842</v>
       </c>
       <c r="E23">
-        <v>-28.15846101906257</v>
+        <v>-32.49674591112179</v>
       </c>
       <c r="F23">
-        <v>3.402007918662484</v>
+        <v>1.254790931803203</v>
       </c>
       <c r="G23">
-        <v>-3.18813595807943</v>
+        <v>-10.03290404598266</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.093689220887892</v>
       </c>
       <c r="E24">
-        <v>-27.68774425986127</v>
+        <v>-33.36917680683252</v>
       </c>
       <c r="F24">
-        <v>3.499795424117208</v>
+        <v>1.079766088852497</v>
       </c>
       <c r="G24">
-        <v>-3.52649357546618</v>
+        <v>-9.969785184730917</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.263897416305465</v>
       </c>
       <c r="E25">
-        <v>-28.28659871958362</v>
+        <v>-34.58597777269355</v>
       </c>
       <c r="F25">
-        <v>3.61829780294588</v>
+        <v>1.17516853319857</v>
       </c>
       <c r="G25">
-        <v>-2.510507012737089</v>
+        <v>-9.546051908431901</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.506069088418337</v>
       </c>
       <c r="E26">
-        <v>-28.6051044104391</v>
+        <v>-35.65731509648018</v>
       </c>
       <c r="F26">
-        <v>3.533233790815796</v>
+        <v>0.9264110939427492</v>
       </c>
       <c r="G26">
-        <v>-3.40480454253365</v>
+        <v>-8.554109837954536</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.805958165605341</v>
       </c>
       <c r="E27">
-        <v>-28.63823019780521</v>
+        <v>-35.62366174189218</v>
       </c>
       <c r="F27">
-        <v>3.255410596893916</v>
+        <v>1.315712930958328</v>
       </c>
       <c r="G27">
-        <v>-2.81329612884991</v>
+        <v>-9.966573955557823</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-2.149263075566033</v>
       </c>
       <c r="E28">
-        <v>-28.66440930604355</v>
+        <v>-34.45002166179826</v>
       </c>
       <c r="F28">
-        <v>3.50949720655519</v>
+        <v>0.6739937103163484</v>
       </c>
       <c r="G28">
-        <v>-3.474455110134377</v>
+        <v>-10.11023176868896</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.517929629902998</v>
       </c>
       <c r="E29">
-        <v>-28.58952645985272</v>
+        <v>-33.98012229215534</v>
       </c>
       <c r="F29">
-        <v>3.50036080712902</v>
+        <v>0.5165551297036397</v>
       </c>
       <c r="G29">
-        <v>-2.933406031560208</v>
+        <v>-8.914807016640289</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.892725739355114</v>
       </c>
       <c r="E30">
-        <v>-27.08807014634354</v>
+        <v>-33.41419210270576</v>
       </c>
       <c r="F30">
-        <v>3.317162457948731</v>
+        <v>1.167592084099107</v>
       </c>
       <c r="G30">
-        <v>-3.141099727057465</v>
+        <v>-7.691057236957616</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-3.259421515767925</v>
       </c>
       <c r="E31">
-        <v>-28.15036863601087</v>
+        <v>-35.73705699528125</v>
       </c>
       <c r="F31">
-        <v>3.650288662437757</v>
+        <v>0.6679281166602153</v>
       </c>
       <c r="G31">
-        <v>-3.07452796680826</v>
+        <v>-9.1433273541251</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.604930172514867</v>
       </c>
       <c r="E32">
-        <v>-28.25642549727051</v>
+        <v>-32.79152239817709</v>
       </c>
       <c r="F32">
-        <v>3.475444361961411</v>
+        <v>0.8302152129330418</v>
       </c>
       <c r="G32">
-        <v>-3.083125453573747</v>
+        <v>-8.693934039351195</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-3.917610174093006</v>
       </c>
       <c r="E33">
-        <v>-27.62155155529116</v>
+        <v>-35.33458886784955</v>
       </c>
       <c r="F33">
-        <v>3.569367624982463</v>
+        <v>0.5263289707607743</v>
       </c>
       <c r="G33">
-        <v>-3.538063932125934</v>
+        <v>-9.716256986242451</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.185667972950793</v>
       </c>
       <c r="E34">
-        <v>-27.91996440697461</v>
+        <v>-32.64167519326327</v>
       </c>
       <c r="F34">
-        <v>3.615858895836103</v>
+        <v>1.09674975108967</v>
       </c>
       <c r="G34">
-        <v>-3.545148499579974</v>
+        <v>-8.048331311555764</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.402594299898488</v>
       </c>
       <c r="E35">
-        <v>-26.62570389321238</v>
+        <v>-33.74517147521538</v>
       </c>
       <c r="F35">
-        <v>3.834533841228152</v>
+        <v>0.8959817684834958</v>
       </c>
       <c r="G35">
-        <v>-4.01398133776048</v>
+        <v>-10.80644611668877</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.565632327554869</v>
       </c>
       <c r="E36">
-        <v>-26.06302288386331</v>
+        <v>-33.51057840772202</v>
       </c>
       <c r="F36">
-        <v>3.117016871767325</v>
+        <v>0.8457814583758961</v>
       </c>
       <c r="G36">
-        <v>-3.362624881817796</v>
+        <v>-9.779779734049987</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-4.676223324470849</v>
       </c>
       <c r="E37">
-        <v>-26.45882509755572</v>
+        <v>-32.81926156571107</v>
       </c>
       <c r="F37">
-        <v>3.222463179029114</v>
+        <v>1.338708340850509</v>
       </c>
       <c r="G37">
-        <v>-2.964220589439744</v>
+        <v>-9.049420419358134</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-4.737884353630718</v>
       </c>
       <c r="E38">
-        <v>-25.41965805311957</v>
+        <v>-33.94661384873558</v>
       </c>
       <c r="F38">
-        <v>3.111169829527522</v>
+        <v>1.503795429181832</v>
       </c>
       <c r="G38">
-        <v>-3.743112501737312</v>
+        <v>-10.80695594070182</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.75447793546176</v>
       </c>
       <c r="E39">
-        <v>-26.37762503012418</v>
+        <v>-32.15573596868519</v>
       </c>
       <c r="F39">
-        <v>3.503461703311451</v>
+        <v>1.218881983876529</v>
       </c>
       <c r="G39">
-        <v>-4.365948607859176</v>
+        <v>-10.10879168137937</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.735763990166389</v>
       </c>
       <c r="E40">
-        <v>-24.40146690028696</v>
+        <v>-30.76058558250607</v>
       </c>
       <c r="F40">
-        <v>3.88680405496723</v>
+        <v>1.871408413685468</v>
       </c>
       <c r="G40">
-        <v>-4.203695460433956</v>
+        <v>-10.28216495127101</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.692539009345963</v>
       </c>
       <c r="E41">
-        <v>-24.60609505527156</v>
+        <v>-31.15897808333087</v>
       </c>
       <c r="F41">
-        <v>3.409216947989564</v>
+        <v>1.660528468809213</v>
       </c>
       <c r="G41">
-        <v>-4.382309323914254</v>
+        <v>-10.86286443376903</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-4.636850495044327</v>
       </c>
       <c r="E42">
-        <v>-23.44657928560756</v>
+        <v>-28.63931250309304</v>
       </c>
       <c r="F42">
-        <v>3.379674497842957</v>
+        <v>1.223387627205955</v>
       </c>
       <c r="G42">
-        <v>-3.242084608187393</v>
+        <v>-10.64427242235649</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.577801666900533</v>
       </c>
       <c r="E43">
-        <v>-22.79737725186794</v>
+        <v>-29.77319710987362</v>
       </c>
       <c r="F43">
-        <v>3.680033826941541</v>
+        <v>1.720953184306889</v>
       </c>
       <c r="G43">
-        <v>-4.192982535068873</v>
+        <v>-9.223462419448699</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.523857488225928</v>
       </c>
       <c r="E44">
-        <v>-20.90433473396749</v>
+        <v>-28.84631810693167</v>
       </c>
       <c r="F44">
-        <v>3.699746214471015</v>
+        <v>1.609571147274033</v>
       </c>
       <c r="G44">
-        <v>-4.164157615058439</v>
+        <v>-11.64029308493824</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.483223485769153</v>
       </c>
       <c r="E45">
-        <v>-20.4367562072535</v>
+        <v>-29.14862091778771</v>
       </c>
       <c r="F45">
-        <v>3.26852526557967</v>
+        <v>1.45513764863587</v>
       </c>
       <c r="G45">
-        <v>-4.81498438371484</v>
+        <v>-10.88541918052808</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.464795165465552</v>
       </c>
       <c r="E46">
-        <v>-20.94330225280349</v>
+        <v>-28.83359762344412</v>
       </c>
       <c r="F46">
-        <v>3.482830766351021</v>
+        <v>1.483246844929005</v>
       </c>
       <c r="G46">
-        <v>-4.460848706287924</v>
+        <v>-10.57890239013804</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.472772860555467</v>
       </c>
       <c r="E47">
-        <v>-21.34650852149845</v>
+        <v>-29.14990700440589</v>
       </c>
       <c r="F47">
-        <v>3.862403897928055</v>
+        <v>1.301381976129516</v>
       </c>
       <c r="G47">
-        <v>-4.592310469652382</v>
+        <v>-11.378902340794</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-4.504789069702455</v>
       </c>
       <c r="E48">
-        <v>-21.79655732532874</v>
+        <v>-27.01987585626203</v>
       </c>
       <c r="F48">
-        <v>3.812309696116789</v>
+        <v>1.383695091084482</v>
       </c>
       <c r="G48">
-        <v>-4.174509690959741</v>
+        <v>-12.45705763820507</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-4.560268658983769</v>
       </c>
       <c r="E49">
-        <v>-19.49268711697843</v>
+        <v>-26.95466583055158</v>
       </c>
       <c r="F49">
-        <v>4.031124007629397</v>
+        <v>1.649950896999992</v>
       </c>
       <c r="G49">
-        <v>-4.057617638513614</v>
+        <v>-10.90132304129874</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-4.636002652923637</v>
       </c>
       <c r="E50">
-        <v>-18.72254312791596</v>
+        <v>-26.99265519900193</v>
       </c>
       <c r="F50">
-        <v>3.376267946418847</v>
+        <v>1.412209716091969</v>
       </c>
       <c r="G50">
-        <v>-4.675514410690885</v>
+        <v>-11.21258384344656</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-4.729039271118843</v>
       </c>
       <c r="E51">
-        <v>-18.74691537502524</v>
+        <v>-26.66469405441842</v>
       </c>
       <c r="F51">
-        <v>3.867392571561689</v>
+        <v>1.686843326300154</v>
       </c>
       <c r="G51">
-        <v>-4.910053319966091</v>
+        <v>-10.34568769907854</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.831670179944862</v>
       </c>
       <c r="E52">
-        <v>-18.10797033491299</v>
+        <v>-23.97902820248143</v>
       </c>
       <c r="F52">
-        <v>3.883856778258598</v>
+        <v>1.872412483235856</v>
       </c>
       <c r="G52">
-        <v>-4.445001124791432</v>
+        <v>-11.54714426509976</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.934422931142031</v>
       </c>
       <c r="E53">
-        <v>-18.04554079224325</v>
+        <v>-26.98725725798478</v>
       </c>
       <c r="F53">
-        <v>3.759488352719138</v>
+        <v>2.276699345623323</v>
       </c>
       <c r="G53">
-        <v>-4.283125379557688</v>
+        <v>-12.20732994599568</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.030259255980244</v>
       </c>
       <c r="E54">
-        <v>-17.75163830067143</v>
+        <v>-25.44598207252616</v>
       </c>
       <c r="F54">
-        <v>3.666794045488467</v>
+        <v>1.437284531851122</v>
       </c>
       <c r="G54">
-        <v>-5.994078214618284</v>
+        <v>-10.74908429412982</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.114833042979712</v>
       </c>
       <c r="E55">
-        <v>-16.70581892791802</v>
+        <v>-23.40056998968963</v>
       </c>
       <c r="F55">
-        <v>4.018744178488406</v>
+        <v>1.957319708480311</v>
       </c>
       <c r="G55">
-        <v>-4.791075623830224</v>
+        <v>-10.62254200143671</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.183681576312141</v>
       </c>
       <c r="E56">
-        <v>-16.10148048617238</v>
+        <v>-23.57673668553602</v>
       </c>
       <c r="F56">
-        <v>3.727149077925864</v>
+        <v>2.157403530131015</v>
       </c>
       <c r="G56">
-        <v>-5.930442908262414</v>
+        <v>-10.82615048373851</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.230453509603005</v>
       </c>
       <c r="E57">
-        <v>-15.55874287635309</v>
+        <v>-22.24138027015419</v>
       </c>
       <c r="F57">
-        <v>4.147999920482913</v>
+        <v>1.767765947461364</v>
       </c>
       <c r="G57">
-        <v>-5.344853750002891</v>
+        <v>-11.63338397639778</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.252824953822033</v>
       </c>
       <c r="E58">
-        <v>-14.93692905341186</v>
+        <v>-23.97223096299591</v>
       </c>
       <c r="F58">
-        <v>3.269860329666386</v>
+        <v>1.876614055029517</v>
       </c>
       <c r="G58">
-        <v>-5.612104159751635</v>
+        <v>-11.39848752820433</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.24979309169855</v>
       </c>
       <c r="E59">
-        <v>-14.63188198730717</v>
+        <v>-21.59604555321711</v>
       </c>
       <c r="F59">
-        <v>3.837089942575671</v>
+        <v>1.386990783094511</v>
       </c>
       <c r="G59">
-        <v>-5.312023069889938</v>
+        <v>-12.55337133957908</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.225282375938396</v>
       </c>
       <c r="E60">
-        <v>-14.5352534089315</v>
+        <v>-23.83528990900396</v>
       </c>
       <c r="F60">
-        <v>3.808142965853269</v>
+        <v>1.904778681029692</v>
       </c>
       <c r="G60">
-        <v>-5.711294725199279</v>
+        <v>-11.71050644528064</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.181249800127358</v>
       </c>
       <c r="E61">
-        <v>-14.57996303280923</v>
+        <v>-21.55281221186588</v>
       </c>
       <c r="F61">
-        <v>3.864494389736435</v>
+        <v>1.728802030823807</v>
       </c>
       <c r="G61">
-        <v>-6.090818976366867</v>
+        <v>-11.30246515483777</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.118239485200777</v>
       </c>
       <c r="E62">
-        <v>-14.08898588089761</v>
+        <v>-21.2112203605193</v>
       </c>
       <c r="F62">
-        <v>3.787850941958743</v>
+        <v>0.9552709668398023</v>
       </c>
       <c r="G62">
-        <v>-5.785364871094933</v>
+        <v>-12.56522640315521</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.039755717743936</v>
       </c>
       <c r="E63">
-        <v>-13.55564032617023</v>
+        <v>-20.31692372806253</v>
       </c>
       <c r="F63">
-        <v>3.487075098204398</v>
+        <v>2.021442377290539</v>
       </c>
       <c r="G63">
-        <v>-6.064284953869609</v>
+        <v>-13.1327896409534</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.949380793465252</v>
       </c>
       <c r="E64">
-        <v>-12.45575097376523</v>
+        <v>-21.00560046972701</v>
       </c>
       <c r="F64">
-        <v>3.728667851898771</v>
+        <v>1.079443012845748</v>
       </c>
       <c r="G64">
-        <v>-6.714678041060365</v>
+        <v>-11.92813177739571</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.85059019215793</v>
       </c>
       <c r="E65">
-        <v>-11.76500924795324</v>
+        <v>-20.19219143999526</v>
       </c>
       <c r="F65">
-        <v>3.636011553610071</v>
+        <v>1.141489443200834</v>
       </c>
       <c r="G65">
-        <v>-5.923245782260038</v>
+        <v>-11.68722999959402</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.743282889906773</v>
       </c>
       <c r="E66">
-        <v>-12.64943380707329</v>
+        <v>-21.89079486942836</v>
       </c>
       <c r="F66">
-        <v>3.147424025343762</v>
+        <v>0.7104268649010329</v>
       </c>
       <c r="G66">
-        <v>-6.065324465168939</v>
+        <v>-12.63756513373383</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.627143077923548</v>
       </c>
       <c r="E67">
-        <v>-12.92093846620316</v>
+        <v>-21.24600809784622</v>
       </c>
       <c r="F67">
-        <v>3.592637015998015</v>
+        <v>0.5523809330697532</v>
       </c>
       <c r="G67">
-        <v>-7.023558560965445</v>
+        <v>-13.40786618035699</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.500910086039445</v>
       </c>
       <c r="E68">
-        <v>-11.96692031853324</v>
+        <v>-17.46757165464428</v>
       </c>
       <c r="F68">
-        <v>3.172060154564338</v>
+        <v>0.6782617977584577</v>
       </c>
       <c r="G68">
-        <v>-7.388440269212837</v>
+        <v>-11.31446257187209</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.368111731173709</v>
       </c>
       <c r="E69">
-        <v>-12.8543064996543</v>
+        <v>-20.1695445414829</v>
       </c>
       <c r="F69">
-        <v>3.218028802465883</v>
+        <v>0.9189914317289155</v>
       </c>
       <c r="G69">
-        <v>-6.049430536034898</v>
+        <v>-13.10708325484096</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.229268860493592</v>
       </c>
       <c r="E70">
-        <v>-12.63721598420059</v>
+        <v>-19.14772155249613</v>
       </c>
       <c r="F70">
-        <v>2.97955119830718</v>
+        <v>1.133577248447299</v>
       </c>
       <c r="G70">
-        <v>-7.173191908794964</v>
+        <v>-11.54893527023651</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.082996801273057</v>
       </c>
       <c r="E71">
-        <v>-12.34641096885003</v>
+        <v>-21.93655509927587</v>
       </c>
       <c r="F71">
-        <v>2.96097274421316</v>
+        <v>1.209332237206429</v>
       </c>
       <c r="G71">
-        <v>-6.318077996001216</v>
+        <v>-12.53596780167913</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.930615036031195</v>
       </c>
       <c r="E72">
-        <v>-12.25558789415219</v>
+        <v>-19.27685098882485</v>
       </c>
       <c r="F72">
-        <v>2.837240968451707</v>
+        <v>1.245002045539872</v>
       </c>
       <c r="G72">
-        <v>-6.423548666336857</v>
+        <v>-12.19743141483326</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.774262569625085</v>
       </c>
       <c r="E73">
-        <v>-12.45484075048969</v>
+        <v>-19.41958848954662</v>
       </c>
       <c r="F73">
-        <v>2.944324827630061</v>
+        <v>0.06676443710080913</v>
       </c>
       <c r="G73">
-        <v>-5.713492927437355</v>
+        <v>-12.2812113907956</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.618864497682134</v>
       </c>
       <c r="E74">
-        <v>-13.234929268473</v>
+        <v>-21.41221215087574</v>
       </c>
       <c r="F74">
-        <v>2.062143619317333</v>
+        <v>0.1807287066287895</v>
       </c>
       <c r="G74">
-        <v>-6.992346737621197</v>
+        <v>-10.62107211921728</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.466741455050798</v>
       </c>
       <c r="E75">
-        <v>-13.08681646910413</v>
+        <v>-22.47737263611591</v>
       </c>
       <c r="F75">
-        <v>2.810126339473468</v>
+        <v>-0.1813072574936259</v>
       </c>
       <c r="G75">
-        <v>-6.499327053730775</v>
+        <v>-11.99703085115902</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.320148393622871</v>
       </c>
       <c r="E76">
-        <v>-12.66812734777695</v>
+        <v>-17.92712572541668</v>
       </c>
       <c r="F76">
-        <v>2.762627831657609</v>
+        <v>0.5477984800034291</v>
       </c>
       <c r="G76">
-        <v>-6.234003381485885</v>
+        <v>-13.30670252976794</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.182982659392656</v>
       </c>
       <c r="E77">
-        <v>-12.93988107297725</v>
+        <v>-20.48890611392584</v>
       </c>
       <c r="F77">
-        <v>1.971023515766609</v>
+        <v>-0.1613216806937378</v>
       </c>
       <c r="G77">
-        <v>-5.831126542084278</v>
+        <v>-11.96211121681079</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.062895576090886</v>
       </c>
       <c r="E78">
-        <v>-13.66260741070541</v>
+        <v>-20.44352627589497</v>
       </c>
       <c r="F78">
-        <v>2.325453732230126</v>
+        <v>0.2487274956670553</v>
       </c>
       <c r="G78">
-        <v>-5.484519045213664</v>
+        <v>-11.16854034559209</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.966729851520291</v>
       </c>
       <c r="E79">
-        <v>-14.16375098676425</v>
+        <v>-21.32545111736278</v>
       </c>
       <c r="F79">
-        <v>2.062590224385487</v>
+        <v>-0.1412197015090649</v>
       </c>
       <c r="G79">
-        <v>-5.170662775363058</v>
+        <v>-9.573095754942207</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.89809669482669</v>
       </c>
       <c r="E80">
-        <v>-15.83309141715979</v>
+        <v>-22.87656214836606</v>
       </c>
       <c r="F80">
-        <v>2.554126613066344</v>
+        <v>0.01398506190991639</v>
       </c>
       <c r="G80">
-        <v>-5.28030473307818</v>
+        <v>-10.34879630133992</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.863786851305718</v>
       </c>
       <c r="E81">
-        <v>-15.9978146591888</v>
+        <v>-21.96070545115878</v>
       </c>
       <c r="F81">
-        <v>2.344268158505547</v>
+        <v>-0.01354370616520981</v>
       </c>
       <c r="G81">
-        <v>-5.423737429112644</v>
+        <v>-11.17229119368809</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.871442671559667</v>
       </c>
       <c r="E82">
-        <v>-15.95912790574127</v>
+        <v>-20.3698615892122</v>
       </c>
       <c r="F82">
-        <v>1.698912749081718</v>
+        <v>-0.4662302050344215</v>
       </c>
       <c r="G82">
-        <v>-4.450579394025104</v>
+        <v>-9.691060424143059</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.932352074522983</v>
       </c>
       <c r="E83">
-        <v>-17.20497450388749</v>
+        <v>-23.30369234524354</v>
       </c>
       <c r="F83">
-        <v>1.883154760460282</v>
+        <v>0.2593921713016246</v>
       </c>
       <c r="G83">
-        <v>-5.424260495307849</v>
+        <v>-10.5528417756529</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.054316526654803</v>
       </c>
       <c r="E84">
-        <v>-17.99221348232892</v>
+        <v>-23.6577873133253</v>
       </c>
       <c r="F84">
-        <v>1.848291058437798</v>
+        <v>-0.3755852132583292</v>
       </c>
       <c r="G84">
-        <v>-4.732379651418946</v>
+        <v>-9.558761092757164</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.240475653108398</v>
       </c>
       <c r="E85">
-        <v>-18.9149172322358</v>
+        <v>-24.97880657999886</v>
       </c>
       <c r="F85">
-        <v>1.528968434707742</v>
+        <v>0.07321328758847856</v>
       </c>
       <c r="G85">
-        <v>-5.145307307077781</v>
+        <v>-11.39495517611393</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.499467867763096</v>
       </c>
       <c r="E86">
-        <v>-19.12771928280425</v>
+        <v>-25.60591418905506</v>
       </c>
       <c r="F86">
-        <v>1.974837079610987</v>
+        <v>0.07887345253025915</v>
       </c>
       <c r="G86">
-        <v>-3.406535957850689</v>
+        <v>-9.780107478058374</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.837799513409335</v>
       </c>
       <c r="E87">
-        <v>-21.59944643719687</v>
+        <v>-27.13932794363636</v>
       </c>
       <c r="F87">
-        <v>1.327858371623833</v>
+        <v>-0.8161009321673888</v>
       </c>
       <c r="G87">
-        <v>-3.055469156138676</v>
+        <v>-9.047281806939765</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.25922502523858</v>
       </c>
       <c r="E88">
-        <v>-22.33316338134165</v>
+        <v>-27.12439303635906</v>
       </c>
       <c r="F88">
-        <v>1.493536182261615</v>
+        <v>-1.111416157925298</v>
       </c>
       <c r="G88">
-        <v>-3.129522749306633</v>
+        <v>-7.981170274200569</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.758283640793803</v>
       </c>
       <c r="E89">
-        <v>-23.88452347841535</v>
+        <v>-29.87987890054632</v>
       </c>
       <c r="F89">
-        <v>1.505998364110208</v>
+        <v>-0.749684265338647</v>
       </c>
       <c r="G89">
-        <v>-2.968792452829478</v>
+        <v>-6.655733777733642</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-5.328395761965912</v>
       </c>
       <c r="E90">
-        <v>-25.187890753407</v>
+        <v>-29.85938302718761</v>
       </c>
       <c r="F90">
-        <v>1.277564622867223</v>
+        <v>-1.138670153024095</v>
       </c>
       <c r="G90">
-        <v>-3.329787580613765</v>
+        <v>-7.029530785118291</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-5.962598572475983</v>
       </c>
       <c r="E91">
-        <v>-26.79536770038376</v>
+        <v>-31.53378629152372</v>
       </c>
       <c r="F91">
-        <v>1.482641869269308</v>
+        <v>-1.349385392485145</v>
       </c>
       <c r="G91">
-        <v>-2.372602927753208</v>
+        <v>-8.689749509789555</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.651681901284324</v>
       </c>
       <c r="E92">
-        <v>-28.09369478380487</v>
+        <v>-33.45777640079259</v>
       </c>
       <c r="F92">
-        <v>0.8983018976496145</v>
+        <v>-0.9978201000226573</v>
       </c>
       <c r="G92">
-        <v>-3.258067922050994</v>
+        <v>-9.481231426772972</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-7.381252285620184</v>
       </c>
       <c r="E93">
-        <v>-29.4208999459729</v>
+        <v>-35.41624404691886</v>
       </c>
       <c r="F93">
-        <v>0.957450146179447</v>
+        <v>-0.9983585600339067</v>
       </c>
       <c r="G93">
-        <v>-2.465116122848142</v>
+        <v>-8.21055135352559</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.125292392805656</v>
       </c>
       <c r="E94">
-        <v>-31.29299827158787</v>
+        <v>-36.62125739493791</v>
       </c>
       <c r="F94">
-        <v>0.8088731920165798</v>
+        <v>-1.908751905524273</v>
       </c>
       <c r="G94">
-        <v>-2.191794172580373</v>
+        <v>-7.619009834386458</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-8.869843325851633</v>
       </c>
       <c r="E95">
-        <v>-33.53922100582054</v>
+        <v>-36.12731862102527</v>
       </c>
       <c r="F95">
-        <v>0.411853164222107</v>
+        <v>-1.346936983139875</v>
       </c>
       <c r="G95">
-        <v>-1.7339821405001</v>
+        <v>-9.717597757185855</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.598745430310668</v>
       </c>
       <c r="E96">
-        <v>-35.12061167827611</v>
+        <v>-38.56890198818584</v>
       </c>
       <c r="F96">
-        <v>0.4401904141670651</v>
+        <v>-2.0738239486494</v>
       </c>
       <c r="G96">
-        <v>-2.447573542035543</v>
+        <v>-8.428646783107236</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.2942800053705</v>
       </c>
       <c r="E97">
-        <v>-37.10115563518977</v>
+        <v>-40.08397995151009</v>
       </c>
       <c r="F97">
-        <v>0.2186687573920146</v>
+        <v>-2.035099963458032</v>
       </c>
       <c r="G97">
-        <v>-2.873826143489945</v>
+        <v>-7.164415652570356</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.94164347426135</v>
       </c>
       <c r="E98">
-        <v>-40.05123229172362</v>
+        <v>-42.75444371620334</v>
       </c>
       <c r="F98">
-        <v>-0.2217812377215541</v>
+        <v>-2.063768207939317</v>
       </c>
       <c r="G98">
-        <v>-3.538381744497703</v>
+        <v>-7.362118121630092</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.51688823242203</v>
       </c>
       <c r="E99">
-        <v>-42.73105188371672</v>
+        <v>-44.45254222078459</v>
       </c>
       <c r="F99">
-        <v>-0.1397745698612264</v>
+        <v>-1.708437654662872</v>
       </c>
       <c r="G99">
-        <v>-2.993667892011561</v>
+        <v>-8.498913112178268</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-12.0222010083872</v>
       </c>
       <c r="E100">
-        <v>-44.536615604974</v>
+        <v>-44.55685109107727</v>
       </c>
       <c r="F100">
-        <v>-0.2802302800897201</v>
+        <v>-2.717478457920046</v>
       </c>
       <c r="G100">
-        <v>-2.94602583115591</v>
+        <v>-9.369384645728694</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.43738497427649</v>
       </c>
       <c r="E101">
-        <v>-46.06666017489359</v>
+        <v>-48.6041453003516</v>
       </c>
       <c r="F101">
-        <v>-0.4616097430261269</v>
+        <v>-2.408556822789639</v>
       </c>
       <c r="G101">
-        <v>-3.36796810231818</v>
+        <v>-8.564137480392988</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.78682865716882</v>
       </c>
       <c r="E102">
-        <v>-48.57388603703235</v>
+        <v>-51.48794094707219</v>
       </c>
       <c r="F102">
-        <v>-0.935407833601104</v>
+        <v>-3.181307119757332</v>
       </c>
       <c r="G102">
-        <v>-3.965306386696577</v>
+        <v>-9.734488160527217</v>
       </c>
     </row>
   </sheetData>
